--- a/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
+++ b/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-25 12:02:41</t>
+          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-25 14:09:05</t>
         </is>
       </c>
     </row>

--- a/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
+++ b/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-25 14:09:05</t>
+          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-25 16:13:22</t>
         </is>
       </c>
     </row>

--- a/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
+++ b/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-25 16:13:22</t>
+          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-25 18:20:17</t>
         </is>
       </c>
     </row>

--- a/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
+++ b/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-25 18:20:17</t>
+          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-25 22:13:02</t>
         </is>
       </c>
     </row>

--- a/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
+++ b/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-25 22:13:02</t>
+          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-25 22:48:28</t>
         </is>
       </c>
     </row>

--- a/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
+++ b/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-25 22:48:28</t>
+          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-26 19:42:40</t>
         </is>
       </c>
     </row>
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>5751897.220000003</v>
+        <v>6830889.420000001</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>5994564.999999994</v>
+        <v>5764683.659999996</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0</v>
@@ -568,7 +568,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>-242667.7799999919</v>
+        <v>1066205.760000004</v>
       </c>
     </row>
     <row r="6">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>5070036.02</v>
+        <v>5065694.22</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>2128756.179999999</v>
+        <v>2125191.359999999</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>0</v>
@@ -813,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>2941279.84</v>
+        <v>2940502.86</v>
       </c>
     </row>
   </sheetData>

--- a/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
+++ b/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-26 19:42:40</t>
+          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-27 11:15:00</t>
         </is>
       </c>
     </row>

--- a/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
+++ b/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-27 11:15:00</t>
+          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-28 06:00:47</t>
         </is>
       </c>
     </row>

--- a/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
+++ b/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-28 06:00:47</t>
+          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-28 11:11:08</t>
         </is>
       </c>
     </row>

--- a/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
+++ b/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-28 11:11:08</t>
+          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-28 21:19:10</t>
         </is>
       </c>
     </row>
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>6830889.420000001</v>
+        <v>152972</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>5764683.659999996</v>
+        <v>529567.6399999999</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0</v>
@@ -568,7 +568,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>1066205.760000004</v>
+        <v>-376595.6399999999</v>
       </c>
     </row>
     <row r="6">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3793569.619999998</v>
+        <v>3775813.039999998</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>2978277.819999996</v>
+        <v>2985936.219999996</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>0</v>
@@ -603,7 +603,7 @@
         <v>82121.64</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>733170.1600000015</v>
+        <v>707755.1800000016</v>
       </c>
     </row>
     <row r="7">
@@ -623,13 +623,13 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2599444.14</v>
+        <v>2563304.14</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>2549880.68</v>
+        <v>2550350.28</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>62995.52</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>-13432.05999999959</v>
+        <v>-50041.65999999968</v>
       </c>
     </row>
     <row r="8">
@@ -658,13 +658,13 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>31144392.86</v>
+        <v>31145112.86</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>12975966.2</v>
+        <v>12976059.89999999</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>0</v>
@@ -673,7 +673,7 @@
         <v>657152.38</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>17511274.28</v>
+        <v>17511900.58000001</v>
       </c>
     </row>
     <row r="9">
@@ -699,7 +699,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>1092564.92</v>
+        <v>1097592.860000001</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>0</v>
@@ -708,7 +708,7 @@
         <v>46588.66</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>-345495.5800000003</v>
+        <v>-350523.5200000005</v>
       </c>
     </row>
     <row r="10">
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>1107952.359999999</v>
+        <v>1112370.779999999</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>0</v>
@@ -743,7 +743,7 @@
         <v>11735.52</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>-973583.6799999988</v>
+        <v>-978002.0999999992</v>
       </c>
     </row>
     <row r="11">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>331456.86</v>
+        <v>325856.86</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>45630.86</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>-102683.1400000001</v>
+        <v>-108283.1400000001</v>
       </c>
     </row>
     <row r="12">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>5065694.22</v>
+        <v>5076929.819999999</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>2125191.359999999</v>
+        <v>2124138.08</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>0</v>
@@ -813,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>2940502.86</v>
+        <v>2952791.74</v>
       </c>
     </row>
   </sheetData>

--- a/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
+++ b/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-28 21:19:10</t>
+          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-29 06:00:48</t>
         </is>
       </c>
     </row>

--- a/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
+++ b/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-29 06:00:48</t>
+          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-29 10:37:37</t>
         </is>
       </c>
     </row>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>5076929.819999999</v>
+        <v>5089836.679999998</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>2124138.08</v>
+        <v>2122809.819999999</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>0</v>
@@ -813,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>2952791.74</v>
+        <v>2967026.859999998</v>
       </c>
     </row>
   </sheetData>

--- a/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
+++ b/CPA_TAX_K1_RECONCILIATION_EXPORT.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-29 10:37:37</t>
+          <t>Tax Year 2026 Preparation Schedule — Generated 2026-10-30 06:00:46</t>
         </is>
       </c>
     </row>
